--- a/data/trans_orig/P33B5_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B5_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que toma algún remedio para dormir (no medicamentos) en 2023</t>
+          <t>Población según la frecuencia con la que toma algún remedio para dormir (no medicamentos) en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1423</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,47 +780,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>5985</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2935</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>10629</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>5985</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>2795</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>11056</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>10496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>294717</t>
+          <t>295095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>307197</t>
+          <t>307827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>273455</t>
+          <t>272873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>281993</t>
+          <t>282244</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>571850</t>
+          <t>572060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>587209</t>
+          <t>587588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23841</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29029</t>
+          <t>27960</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>47810</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39459</t>
+          <t>39685</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64311</t>
+          <t>63770</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17560</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35781</t>
+          <t>35893</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26552</t>
+          <t>26838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47553</t>
+          <t>48187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31337</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57634</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>43983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65227</t>
+          <t>66465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80917</t>
+          <t>80040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116628</t>
+          <t>117282</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>432023</t>
+          <t>432548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>465277</t>
+          <t>465148</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>381213</t>
+          <t>381151</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>413791</t>
+          <t>411385</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>824292</t>
+          <t>821321</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>870677</t>
+          <t>871083</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24350</t>
+          <t>23707</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29258</t>
+          <t>29953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17977</t>
+          <t>17289</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22580</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23359</t>
+          <t>24650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21245</t>
+          <t>21475</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40118</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>286044</t>
+          <t>287144</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302316</t>
+          <t>303108</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>295692</t>
+          <t>297462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>316087</t>
+          <t>315621</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>589916</t>
+          <t>588137</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>615115</t>
+          <t>613954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29030</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41267</t>
+          <t>41714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>34932</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63331</t>
+          <t>63956</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>17554</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25740</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16199</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39453</t>
+          <t>40694</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30754</t>
+          <t>30853</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>59738</t>
+          <t>57547</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>262052</t>
+          <t>262203</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>286641</t>
+          <t>286598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>391411</t>
+          <t>390164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>438837</t>
+          <t>435493</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>663240</t>
+          <t>663997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>712568</t>
+          <t>713840</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12316</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15506</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>12282</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23201</t>
+          <t>23426</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>43920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63110</t>
+          <t>63560</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70314</t>
+          <t>72381</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90004</t>
+          <t>90730</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>121456</t>
+          <t>120754</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>149609</t>
+          <t>149654</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>105764</t>
+          <t>105999</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>127104</t>
+          <t>126805</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>101351</t>
+          <t>101815</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>122174</t>
+          <t>120408</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>212939</t>
+          <t>211911</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>241567</t>
+          <t>241871</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26761</t>
+          <t>26674</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41039</t>
+          <t>41723</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>37806</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57568</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14033</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7955</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16334</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12371</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24850</t>
+          <t>24912</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>236829</t>
+          <t>238291</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>252584</t>
+          <t>252967</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>193058</t>
+          <t>192934</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>211652</t>
+          <t>212656</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>437852</t>
+          <t>436504</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>461188</t>
+          <t>462064</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20315</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>45717</t>
+          <t>45966</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>23482</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>77777</t>
+          <t>78100</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>55200</t>
+          <t>55391</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>109466</t>
+          <t>109861</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>25092</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>29920</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>16360</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>46189</t>
+          <t>42552</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>19522</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>44685</t>
+          <t>42976</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>73872</t>
+          <t>73644</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>49730</t>
+          <t>47820</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>103047</t>
+          <t>102755</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>531820</t>
+          <t>532482</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>570522</t>
+          <t>570661</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>676260</t>
+          <t>677387</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>793955</t>
+          <t>788686</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1234846</t>
+          <t>1237188</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1345383</t>
+          <t>1355568</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>32473</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>104435</t>
+          <t>105464</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>106819</t>
+          <t>106871</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>141396</t>
+          <t>141663</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>118539</t>
+          <t>116217</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>239662</t>
+          <t>240016</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>9621</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35546</t>
+          <t>36188</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>31200</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>49368</t>
+          <t>49193</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>38881</t>
+          <t>38609</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>79287</t>
+          <t>79351</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17991</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>63453</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>49242</t>
+          <t>47973</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>72894</t>
+          <t>72056</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>59776</t>
+          <t>63041</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>127717</t>
+          <t>128000</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>732651</t>
+          <t>731703</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>866842</t>
+          <t>866372</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>473595</t>
+          <t>472891</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>513848</t>
+          <t>513531</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1208412</t>
+          <t>1210449</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1426212</t>
+          <t>1420874</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>123270</t>
+          <t>123287</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>187737</t>
+          <t>187787</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>244754</t>
+          <t>248519</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>338972</t>
+          <t>341741</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>399422</t>
+          <t>399588</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>511220</t>
+          <t>511483</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>43742</t>
+          <t>43843</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>77640</t>
+          <t>77600</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>98196</t>
+          <t>99883</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>143353</t>
+          <t>144928</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>154757</t>
+          <t>158306</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>211162</t>
+          <t>211646</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>166367</t>
+          <t>159730</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>243133</t>
+          <t>242285</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>241716</t>
+          <t>251989</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>339918</t>
+          <t>339486</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>447701</t>
+          <t>445817</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>562403</t>
+          <t>569715</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2978480</t>
+          <t>2979668</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3120159</t>
+          <t>3127077</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2860246</t>
+          <t>2856529</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3076003</t>
+          <t>3061141</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>5862816</t>
+          <t>5868661</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6093833</t>
+          <t>6120779</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B5_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B5_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -838,22 +838,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>302734</t>
+          <t>310317</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>295095</t>
+          <t>303346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>307827</t>
+          <t>314637</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>278162</t>
+          <t>303143</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>272873</t>
+          <t>297637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>282244</t>
+          <t>307227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>580895</t>
+          <t>613460</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>572060</t>
+          <t>605280</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>587588</t>
+          <t>619286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13616</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23100</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>37826</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27960</t>
+          <t>28355</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47810</t>
+          <t>49033</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>50745</t>
+          <t>51776</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39685</t>
+          <t>39700</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>63770</t>
+          <t>65383</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19547</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,27 +1442,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26669</t>
+          <t>28943</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>21494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35893</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1477,22 +1477,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>38850</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26838</t>
+          <t>28003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48187</t>
+          <t>50940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43774</t>
+          <t>44750</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31829</t>
+          <t>32535</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58656</t>
+          <t>60551</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53783</t>
+          <t>55876</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43983</t>
+          <t>45053</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66465</t>
+          <t>68833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>97556</t>
+          <t>100626</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80040</t>
+          <t>84708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117282</t>
+          <t>122143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>450207</t>
+          <t>461054</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>432548</t>
+          <t>443925</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>465148</t>
+          <t>477163</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>396821</t>
+          <t>423252</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>381151</t>
+          <t>407272</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>411385</t>
+          <t>439784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>847028</t>
+          <t>884306</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>821321</t>
+          <t>859456</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>871083</t>
+          <t>905591</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514403</t>
+          <t>545898</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514403</t>
+          <t>545898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514403</t>
+          <t>545898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1031796</t>
+          <t>1075558</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1031796</t>
+          <t>1075558</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1031796</t>
+          <t>1075558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23707</t>
+          <t>25241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>17468</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>21066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24650</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>29784</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>42435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>295886</t>
+          <t>296197</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287144</t>
+          <t>287098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>303108</t>
+          <t>302936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>306806</t>
+          <t>312295</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>297462</t>
+          <t>302271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>315621</t>
+          <t>322232</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>602691</t>
+          <t>608493</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>588137</t>
+          <t>593954</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>613954</t>
+          <t>619870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>21590</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29030</t>
+          <t>33061</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>32844</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41714</t>
+          <t>41944</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>48783</t>
+          <t>54433</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34932</t>
+          <t>43202</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63956</t>
+          <t>68439</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>11663</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17554</t>
+          <t>18412</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>26637</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29386</t>
+          <t>31827</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17698</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40694</t>
+          <t>42759</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>43973</t>
+          <t>47190</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>35824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57547</t>
+          <t>60088</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>275886</t>
+          <t>332483</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>262203</t>
+          <t>316843</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>286598</t>
+          <t>344560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>409802</t>
+          <t>350546</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>390164</t>
+          <t>336665</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>435493</t>
+          <t>362471</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>685688</t>
+          <t>683030</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>663997</t>
+          <t>664365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>713840</t>
+          <t>698380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>87,83%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>13441</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>11662</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15655</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17338</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23426</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>53223</t>
+          <t>58524</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43920</t>
+          <t>48190</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63560</t>
+          <t>70228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>80931</t>
+          <t>85375</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>72381</t>
+          <t>76168</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90730</t>
+          <t>96226</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>134154</t>
+          <t>143900</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>120754</t>
+          <t>128699</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>149654</t>
+          <t>158965</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>116435</t>
+          <t>137626</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>105999</t>
+          <t>125516</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>126805</t>
+          <t>147851</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>111175</t>
+          <t>124133</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>101815</t>
+          <t>113736</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>120408</t>
+          <t>134680</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>227609</t>
+          <t>261759</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>211911</t>
+          <t>245336</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>241871</t>
+          <t>276030</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>63,82%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>13782</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,17 +3605,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>33328</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26674</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41723</t>
+          <t>42784</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,17 +3640,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>47320</t>
+          <t>47990</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37806</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57568</t>
+          <t>57384</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>18251</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,27 +3866,27 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>25291</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>246365</t>
+          <t>247769</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>238291</t>
+          <t>239373</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>252967</t>
+          <t>253956</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>203397</t>
+          <t>208490</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>192934</t>
+          <t>198803</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>212656</t>
+          <t>217968</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>449763</t>
+          <t>456259</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>436504</t>
+          <t>444492</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>462064</t>
+          <t>468117</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>30158</t>
+          <t>32188</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20727</t>
+          <t>22155</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>45966</t>
+          <t>48311</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>54739</t>
+          <t>65099</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>51829</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>78100</t>
+          <t>81176</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>84898</t>
+          <t>97286</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>55391</t>
+          <t>80578</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>109861</t>
+          <t>116671</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25092</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>24624</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>29319</t>
+          <t>35267</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
           <t>2,15%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>28665</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>42552</t>
+          <t>51298</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>34210</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>19522</t>
+          <t>24015</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>42976</t>
+          <t>50222</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>50693</t>
+          <t>58042</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>45679</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>73644</t>
+          <t>73766</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>80276</t>
+          <t>92252</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>47820</t>
+          <t>76153</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>102755</t>
+          <t>113504</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>553057</t>
+          <t>639882</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>532482</t>
+          <t>616191</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>570661</t>
+          <t>656206</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>725030</t>
+          <t>623623</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>677387</t>
+          <t>602175</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>788686</t>
+          <t>643451</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1278086</t>
+          <t>1263506</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1237188</t>
+          <t>1233394</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1355568</t>
+          <t>1289068</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>848675</t>
+          <t>771388</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>848675</t>
+          <t>771388</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>848675</t>
+          <t>771388</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1471924</t>
+          <t>1489993</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1471924</t>
+          <t>1489993</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1471924</t>
+          <t>1489993</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>72372</t>
+          <t>81097</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>66155</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>105464</t>
+          <t>97716</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>123250</t>
+          <t>136399</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>106871</t>
+          <t>118906</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>141663</t>
+          <t>153419</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>195621</t>
+          <t>217496</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>116217</t>
+          <t>195122</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>240016</t>
+          <t>243588</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>25491</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>9621</t>
+          <t>18241</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>36188</t>
+          <t>34481</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>39120</t>
+          <t>45544</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>30898</t>
+          <t>35504</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>49193</t>
+          <t>57904</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>62021</t>
+          <t>71035</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>38609</t>
+          <t>57717</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>79351</t>
+          <t>86032</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>42777</t>
+          <t>51748</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>39376</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>64580</t>
+          <t>68668</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>59361</t>
+          <t>71351</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>47973</t>
+          <t>58457</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>72056</t>
+          <t>85774</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>102138</t>
+          <t>123099</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>63041</t>
+          <t>103498</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>128000</t>
+          <t>143417</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>790670</t>
+          <t>639736</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>731703</t>
+          <t>617718</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>866372</t>
+          <t>661074</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>493662</t>
+          <t>577314</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>472891</t>
+          <t>556754</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>513531</t>
+          <t>603115</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1284332</t>
+          <t>1217050</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1210449</t>
+          <t>1185698</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1420874</t>
+          <t>1251241</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>158650</t>
+          <t>172532</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>123287</t>
+          <t>148542</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>187787</t>
+          <t>200672</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>303951</t>
+          <t>333149</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>248519</t>
+          <t>304805</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>341741</t>
+          <t>362646</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>462601</t>
+          <t>505681</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>399588</t>
+          <t>467921</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>511483</t>
+          <t>542602</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>65044</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>43843</t>
+          <t>50914</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>77600</t>
+          <t>86033</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>123679</t>
+          <t>141087</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>99883</t>
+          <t>123120</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>144928</t>
+          <t>160415</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>183945</t>
+          <t>206131</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>158306</t>
+          <t>183263</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>211646</t>
+          <t>232034</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>207635</t>
+          <t>228051</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>159730</t>
+          <t>198538</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>242285</t>
+          <t>256728</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>305795</t>
+          <t>335839</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>251989</t>
+          <t>306691</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>339486</t>
+          <t>364410</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>513430</t>
+          <t>563889</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>445817</t>
+          <t>525793</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>569715</t>
+          <t>606382</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>3031240</t>
+          <t>3065066</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2979668</t>
+          <t>3023622</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3127077</t>
+          <t>3107793</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2924853</t>
+          <t>2922798</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2856529</t>
+          <t>2879798</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3061141</t>
+          <t>2963406</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>5956093</t>
+          <t>5987863</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>5868661</t>
+          <t>5926044</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6120779</t>
+          <t>6042201</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
